--- a/data/trans_dic/P64D$particular_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,27; 88,16</t>
+          <t>73,83; 88,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,36; 49,66</t>
+          <t>26,78; 48,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,83; 72,44</t>
+          <t>58,11; 71,75</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,18; 89,61</t>
+          <t>76,02; 89,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,55; 64,67</t>
+          <t>44,68; 64,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,41; 79,08</t>
+          <t>65,77; 79,91</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,92; 71,53</t>
+          <t>62,34; 72,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,8; 71,44</t>
+          <t>63,47; 71,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,09; 70,19</t>
+          <t>64,04; 70,52</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,18; 85,21</t>
+          <t>74,28; 85,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,2; 64,41</t>
+          <t>50,75; 64,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,16; 76,97</t>
+          <t>66,09; 76,37</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98111; 116457</t>
+          <t>97527; 116942</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22815; 39949</t>
+          <t>21544; 38740</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>125050; 153972</t>
+          <t>123510; 152505</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1053040; 1238822</t>
+          <t>1050924; 1242083</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>430456; 611084</t>
+          <t>422234; 613816</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1522400; 1840389</t>
+          <t>1530667; 1859802</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>276970; 319954</t>
+          <t>278834; 323532</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>277758; 311005</t>
+          <t>276325; 311402</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>565724; 619556</t>
+          <t>565212; 622478</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1455224; 1671641</t>
+          <t>1457141; 1677773</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>733245; 940900</t>
+          <t>741351; 937684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2264430; 2634305</t>
+          <t>2261899; 2613729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$particular_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,83; 88,52</t>
+          <t>64,8; 81,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,78; 48,16</t>
+          <t>30,08; 49,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,11; 71,75</t>
+          <t>55,03; 68,05</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,02; 89,85</t>
+          <t>72,45; 78,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,68; 64,96</t>
+          <t>57,32; 63,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,77; 79,91</t>
+          <t>66,96; 71,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,34; 72,33</t>
+          <t>60,94; 70,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,47; 71,53</t>
+          <t>62,59; 70,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,04; 70,52</t>
+          <t>62,96; 69,13</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,28; 85,52</t>
+          <t>70,72; 75,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,75; 64,19</t>
+          <t>58,63; 63,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,09; 76,37</t>
+          <t>65,95; 69,29</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>108750</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139179</t>
+          <t>156006</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97527; 116942</t>
+          <t>106222; 134085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21544; 38740</t>
+          <t>26467; 43212</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123510; 152505</t>
+          <t>138634; 171446</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1120997</t>
+          <t>959282</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>554785</t>
+          <t>568276</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1675783</t>
+          <t>1527559</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1050924; 1242083</t>
+          <t>920546; 994937</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422234; 613816</t>
+          <t>541795; 598629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1530667; 1859802</t>
+          <t>1483646; 1575191</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>299903</t>
+          <t>322279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>294429</t>
+          <t>317276</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>594332</t>
+          <t>639555</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>278834; 323532</t>
+          <t>297147; 344168</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>276325; 311402</t>
+          <t>298869; 334253</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>565212; 622478</t>
+          <t>607638; 667138</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1529650</t>
+          <t>1403226</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879643</t>
+          <t>919894</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2409294</t>
+          <t>2323120</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1457141; 1677773</t>
+          <t>1359288; 1447380</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>741351; 937684</t>
+          <t>885682; 956010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2261899; 2613729</t>
+          <t>2263791; 2378561</t>
         </is>
       </c>
     </row>
